--- a/data/trans_orig/IP36A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>62834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68896</t>
+          <t>69294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68473</t>
+          <t>68528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75109</t>
+          <t>75158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134126</t>
+          <t>134472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143158</t>
+          <t>143083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81524</t>
+          <t>80697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87520</t>
+          <t>87535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88131</t>
+          <t>87921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>96930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172522</t>
+          <t>172302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182745</t>
+          <t>182801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>57919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65206</t>
+          <t>65141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115959</t>
+          <t>116169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125997</t>
+          <t>126516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>61669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71309</t>
+          <t>71356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61399</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68412</t>
+          <t>68466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125825</t>
+          <t>125731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138177</t>
+          <t>137965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>271085</t>
+          <t>270916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285947</t>
+          <t>285661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>284805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299997</t>
+          <t>299769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>561505</t>
+          <t>561257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>582048</t>
+          <t>581438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72742</t>
+          <t>73239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79940</t>
+          <t>80152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78538</t>
+          <t>78571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87256</t>
+          <t>87223</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155578</t>
+          <t>155703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165899</t>
+          <t>166166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20910</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96352</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107427</t>
+          <t>107870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108002</t>
+          <t>108687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119029</t>
+          <t>119213</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208253</t>
+          <t>209211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>223140</t>
+          <t>224056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65925</t>
+          <t>67161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75556</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75102</t>
+          <t>75732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85365</t>
+          <t>86012</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145300</t>
+          <t>145817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159070</t>
+          <t>159380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>30764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87903</t>
+          <t>86871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98878</t>
+          <t>98632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85853</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96607</t>
+          <t>96240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178140</t>
+          <t>177336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192941</t>
+          <t>192548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>53201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67089</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>95421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335276</t>
+          <t>335880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354515</t>
+          <t>354238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361104</t>
+          <t>359882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380795</t>
+          <t>380921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>702879</t>
+          <t>701864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730196</t>
+          <t>730669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>67426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73934</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69989</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77846</t>
+          <t>77869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141393</t>
+          <t>140992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150595</t>
+          <t>150581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31940</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93328</t>
+          <t>92932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102617</t>
+          <t>103248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100590</t>
+          <t>102172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112582</t>
+          <t>112902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199167</t>
+          <t>198836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213794</t>
+          <t>213551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27192</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65018</t>
+          <t>64980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73118</t>
+          <t>73149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>61014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71680</t>
+          <t>71577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128913</t>
+          <t>130034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>143356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16697</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32235</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>80942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90710</t>
+          <t>90532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62032</t>
+          <t>61972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>74762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147022</t>
+          <t>146847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162560</t>
+          <t>162644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62753</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>89457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>318887</t>
+          <t>318533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335070</t>
+          <t>334672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>308348</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>329795</t>
+          <t>329003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>631980</t>
+          <t>631673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>658377</t>
+          <t>659597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45247</t>
+          <t>45481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>37166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>75121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88651</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19889</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54649</t>
+          <t>54320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>61935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61194</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73073</t>
+          <t>72833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119548</t>
+          <t>118148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133786</t>
+          <t>133083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25846</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39876</t>
+          <t>40449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67216</t>
+          <t>67020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88475</t>
+          <t>88179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57629</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118700</t>
+          <t>118127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144239</t>
+          <t>143102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33750</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40603</t>
+          <t>40340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53382</t>
+          <t>52709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>78312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94698</t>
+          <t>94010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>55108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61063</t>
+          <t>60364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70319</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109177</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>205170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233550</t>
+          <t>232192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196825</t>
+          <t>197524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219708</t>
+          <t>220050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>408990</t>
+          <t>410686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447848</t>
+          <t>447906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP36A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7895</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>3845</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7817</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3993</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1379</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8009</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72544</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>68642</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75201</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66806</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>62834</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69294</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62873</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69196</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72544</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>68528</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>75158</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134472</t>
+          <t>134244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143083</t>
+          <t>143220</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70651</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70651</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70651</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7773</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13151</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8117</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7589</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7773</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3972</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12981</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93129</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>87751</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>96556</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>85110</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80697</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>87535</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>81225</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>87531</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,83%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>98,56%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93129</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>87921</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>96930</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>276</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172302</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182801</t>
+          <t>183278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>100902</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>100902</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>100902</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>88814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>88814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>100902</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>100902</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>100902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5655</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9992</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6036</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3084</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10213</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2952</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10674</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5655</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9806</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17491</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62070</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57733</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>65212</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>59898</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55721</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>62850</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55260</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>62982</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>62070</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57919</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>65141</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116169</t>
+          <t>115976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126516</t>
+          <t>126394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67725</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>67725</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>67725</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>65934</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>65934</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>65934</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>67725</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>67725</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>67725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9488</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8914</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4733</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14420</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4167</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15282</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4704</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9295</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20823</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65761</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60977</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68425</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>67175</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61669</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71356</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60807</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>71922</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>65761</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>61170</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>68466</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125731</t>
+          <t>126397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137965</t>
+          <t>138795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>70465</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>70465</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>70465</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76089</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76089</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76089</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>70465</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>70465</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>70465</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16332</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30481</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>22499</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15827</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30572</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15685</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>30786</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15861</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30825</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35680</t>
+          <t>35697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>293505</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>285149</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>299298</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>418</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>278989</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>270916</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>285661</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>270702</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>285803</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>293505</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>284805</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>299769</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>561257</t>
+          <t>561461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>581438</t>
+          <t>581421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6653</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3811</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12068</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3997</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1394</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8307</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8942</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6653</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11977</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83895</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78480</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86737</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77549</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>73239</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80152</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72604</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80109</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,1%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83895</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>78571</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87223</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155703</t>
+          <t>155571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166166</t>
+          <t>165991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90548</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>90548</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>90548</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>81546</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>81546</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>81546</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>90548</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>90548</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>90548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12432</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18636</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14745</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9392</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20705</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9476</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20328</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12432</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7426</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17952</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>114207</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108003</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118851</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>102517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>96557</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>107870</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>96934</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>107786</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>87,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>114207</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>108687</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>119213</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,18%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209211</t>
+          <t>207434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>224056</t>
+          <t>223722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>126639</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>126639</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>126639</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>117262</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>117262</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>117262</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>126639</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>126639</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>126639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10845</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6375</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16736</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9353</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5461</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13878</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14662</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10845</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16419</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81306</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75415</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85776</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>71686</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67161</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75578</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66377</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75285</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,46%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>81306</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75732</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86012</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145817</t>
+          <t>144782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159380</t>
+          <t>158490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>92151</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>92151</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>92151</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>81039</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>81039</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>81039</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>92151</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>92151</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>92151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11829</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6602</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17413</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10402</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5723</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17484</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16685</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11829</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7505</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18177</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15552</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -3817,67 +3817,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>91916</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>86332</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>97143</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>93953</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86871</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>98632</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>87670</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>98241</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>91916</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>85568</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>96240</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177336</t>
+          <t>177573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192548</t>
+          <t>192519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>103745</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>103745</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>103745</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>104355</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>104355</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>104355</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>103745</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>103745</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>103745</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38497</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29964</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>48322</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30332</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48868</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>41758</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32162</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53201</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>67069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95421</t>
+          <t>96012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>371325</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>360325</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>380190</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>345705</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>335880</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>354238</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>335334</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>353870</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>371325</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>359882</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>380921</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>701864</t>
+          <t>701273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730669</t>
+          <t>730216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>413083</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>413083</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>413083</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>553</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>384202</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>384202</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>384202</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>413083</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>413083</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>413083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,107 +4617,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9482</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2868</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7184</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6818</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5056</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2181</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10016</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>4230</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>13580</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>7924</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>4079</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>13668</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -4730,107 +4730,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74994</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70568</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77875</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>71742</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67426</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73939</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67792</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73933</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74994</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>70034</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>146736</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>150430</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>97,27%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>146736</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>140992</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>150581</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80050</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80050</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80050</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>74610</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>74610</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>74610</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80050</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80050</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80050</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12891</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8142</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19586</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11080</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6712</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17028</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7018</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16598</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12891</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8245</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18975</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32271</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108256</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>101561</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>113005</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>98880</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>92932</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>103248</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>93362</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>102942</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108256</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>102172</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112902</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198836</t>
+          <t>199085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213551</t>
+          <t>213799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -5191,52 +5191,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>121147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>121147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>121147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>109960</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>109960</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>109960</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>121147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>121147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>121147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11556</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17779</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7618</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4090</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12259</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4430</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12431</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11556</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7290</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17853</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67311</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61088</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71946</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69621</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64980</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73149</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64808</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>72809</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67311</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61014</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>71577</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130034</t>
+          <t>129138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143356</t>
+          <t>142941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>78867</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>78867</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>78867</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>77239</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>77239</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>77239</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>78867</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>78867</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>78867</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10167</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21996</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8319</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4782</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14372</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14281</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15173</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9182</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21972</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32410</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68771</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61948</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73777</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>86995</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>80942</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90532</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>81033</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>90586</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>68771</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>61972</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>74762</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146847</t>
+          <t>147337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162644</t>
+          <t>163066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95314</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95314</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95314</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34909</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56409</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29884</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22450</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38589</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>22178</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39283</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>44676</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>35004</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>55841</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>63317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89457</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>319331</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>307598</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>329098</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>489</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>327238</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>318533</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>334672</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>317839</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>334944</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>319331</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>308166</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>329003</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>631673</t>
+          <t>630013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>659597</t>
+          <t>657813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>357122</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>357122</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>357122</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5961</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10456</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8479</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14181</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34734</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37685</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41207</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35505</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45481</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,94%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>42506</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37166</t>
+          <t>35068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45371</t>
+          <t>46958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>83209</t>
+          <t>77239</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>69148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>83475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40695</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40695</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40695</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>49686</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>49686</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>49686</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>52024</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12867</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7616</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19855</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5929</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3185</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10800</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21039</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>62768</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55780</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>68019</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>59191</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54320</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61935</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>53792</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60044</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72833</t>
+          <t>57014</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>126958</t>
+          <t>116560</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118148</t>
+          <t>108240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133083</t>
+          <t>122213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>75635</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>75635</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>75635</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>65120</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>65120</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>65120</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81083</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81083</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81083</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>146203</t>
+          <t>135251</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146203</t>
+          <t>135251</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146203</t>
+          <t>135251</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,62 +7250,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7259</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18689</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14497</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4883</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26042</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40449</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -7363,67 +7363,67 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48269</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41681</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53111</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>78565</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67020</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>88179</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>84,42%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52787</t>
+          <t>49104</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57722</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>131352</t>
+          <t>97373</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118127</t>
+          <t>88682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143102</t>
+          <t>104358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93062</t>
+          <t>60370</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93062</t>
+          <t>60370</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93062</t>
+          <t>60370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65514</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65514</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65514</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>158576</t>
+          <t>121211</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>158576</t>
+          <t>121211</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158576</t>
+          <t>121211</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14502</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9636</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20891</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12493</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8308</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18348</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45066</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38677</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49932</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>39918</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34063</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>44103</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47280</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40340</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52709</t>
+          <t>45432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>87199</t>
+          <t>85585</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78312</t>
+          <t>76542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94010</t>
+          <t>92880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59568</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>59568</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>59568</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>52411</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>52411</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>52411</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>115290</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115290</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115290</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45431</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35136</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56314</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28086</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55108</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>85368</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70261</t>
+          <t>71378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107481</t>
+          <t>101591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>190836</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>179953</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>201131</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>218881</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>205170</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>232192</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>84,09%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>209837</t>
+          <t>185920</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197524</t>
+          <t>174381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220050</t>
+          <t>195630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>428719</t>
+          <t>376756</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410686</t>
+          <t>360533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447906</t>
+          <t>390746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
